--- a/Plotting/Results_excels/production_shares_olefins_LowAmbition_FPO.xlsx
+++ b/Plotting/Results_excels/production_shares_olefins_LowAmbition_FPO.xlsx
@@ -539,7 +539,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Conventional</t>
+          <t>Conventional (fossil)</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -573,7 +573,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Carbon Capture</t>
+          <t>Conventional (fossil) with CC</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -620,22 +620,22 @@
         <v>1016974.754263447</v>
       </c>
       <c r="E6" t="n">
-        <v>1717666.256705107</v>
+        <v>1717666.25670495</v>
       </c>
       <c r="F6" t="n">
-        <v>1291314.458533723</v>
+        <v>1289650.901091484</v>
       </c>
       <c r="G6" t="n">
-        <v>1289650.900672366</v>
+        <v>1289650.900672317</v>
       </c>
       <c r="H6" t="n">
-        <v>1717666.256705058</v>
+        <v>1717666.256704886</v>
       </c>
       <c r="I6" t="n">
-        <v>1291259.111577258</v>
+        <v>1290979.602289328</v>
       </c>
       <c r="J6" t="n">
-        <v>1289650.90154509</v>
+        <v>1289650.900678038</v>
       </c>
     </row>
     <row r="7">
@@ -691,19 +691,19 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>426263.3696502685</v>
+        <v>427926.5820583764</v>
       </c>
       <c r="G8" t="n">
-        <v>427926.5824774022</v>
+        <v>427926.5824773982</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>426318.705127371</v>
+        <v>426598.1564429976</v>
       </c>
       <c r="J8" t="n">
-        <v>427926.5824773957</v>
+        <v>427926.5824773998</v>
       </c>
     </row>
     <row r="9">
